--- a/docs/examples/Riverside-timetable.xlsx
+++ b/docs/examples/Riverside-timetable.xlsx
@@ -56,6 +56,39 @@
     <t>Grade 6 A</t>
   </si>
   <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Bilal Ahmed</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Urdu</t>
+  </si>
+  <si>
+    <t>Erum Shah</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
     <t>Physical Education</t>
   </si>
   <si>
@@ -65,19 +98,40 @@
     <t>Playground</t>
   </si>
   <si>
-    <t>Monday</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>Morning</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>Care Fernandes</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Ayesha Khan</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
   </si>
   <si>
     <t>Social Studies</t>
@@ -86,55 +140,7 @@
     <t>Gul Rukh</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t>Care Fernandes</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Ayesha Khan</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>Mathematics</t>
-  </si>
-  <si>
-    <t>Bilal Ahmed</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>Urdu</t>
-  </si>
-  <si>
-    <t>Erum Shah</t>
+    <t>Islamic Studies</t>
   </si>
   <si>
     <t>6</t>
@@ -143,12 +149,6 @@
     <t>12:20</t>
   </si>
   <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>Islamic Studies</t>
-  </si>
-  <si>
     <t>Wednesday</t>
   </si>
   <si>
@@ -192,70 +192,110 @@
   </si>
   <si>
     <t>Morning shift</t>
-  </si>
-  <si>
-    <t>6A</t>
-  </si>
-  <si>
-    <t>PE IQU</t>
-  </si>
-  <si>
-    <t>SST GRU</t>
-  </si>
-  <si>
-    <t>SCI CFE</t>
-  </si>
-  <si>
-    <t>ENG AKH</t>
-  </si>
-  <si>
-    <t>MATH BAH</t>
-  </si>
-  <si>
-    <t>URD ESH</t>
-  </si>
-  <si>
-    <t>ISL IQU</t>
-  </si>
-  <si>
-    <t>COMP HNO</t>
-  </si>
-  <si>
-    <t>ART HNO</t>
-  </si>
-  <si>
-    <t>6B</t>
-  </si>
-  <si>
-    <t>7A</t>
-  </si>
-  <si>
-    <t>URD FIQ</t>
-  </si>
-  <si>
-    <t>ENG DAL</t>
-  </si>
-  <si>
-    <t>7B</t>
-  </si>
-  <si>
-    <t>6C</t>
-  </si>
-  <si>
-    <t>Grade 6 A · Morning shift</t>
-  </si>
-  <si>
-    <t>Period</t>
   </si>
   <si>
     <t>1
 08:00–08:40</t>
   </si>
   <si>
+    <t>2
+08:40–09:20</t>
+  </si>
+  <si>
+    <t>3
+09:20–10:00</t>
+  </si>
+  <si>
+    <t>4
+10:20–11:00</t>
+  </si>
+  <si>
+    <t>5
+11:00–11:40</t>
+  </si>
+  <si>
+    <t>6
+11:40–12:20</t>
+  </si>
+  <si>
+    <t>7
+12:20–13:00</t>
+  </si>
+  <si>
+    <t>6A</t>
+  </si>
+  <si>
+    <t>MATH BAH</t>
+  </si>
+  <si>
+    <t>URD ESH</t>
+  </si>
+  <si>
+    <t>PE IQU</t>
+  </si>
+  <si>
+    <t>SCI CFE</t>
+  </si>
+  <si>
+    <t>ENG AKH</t>
+  </si>
+  <si>
+    <t>SST GRU</t>
+  </si>
+  <si>
+    <t>ISL IQU</t>
+  </si>
+  <si>
+    <t>COMP HNO</t>
+  </si>
+  <si>
+    <t>ART HNO</t>
+  </si>
+  <si>
+    <t>6B</t>
+  </si>
+  <si>
+    <t>7A</t>
+  </si>
+  <si>
+    <t>URD FIQ</t>
+  </si>
+  <si>
+    <t>ENG DAL</t>
+  </si>
+  <si>
+    <t>7B</t>
+  </si>
+  <si>
+    <t>6C</t>
+  </si>
+  <si>
+    <t>Grade 6 A · Morning shift</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Mathematics
+Bilal Ahmed</t>
+  </si>
+  <si>
+    <t>Science
+Care Fernandes</t>
+  </si>
+  <si>
     <t>Physical Education
 Imran Qureshi · Playground</t>
   </si>
   <si>
+    <t>Computer Studies
+Hamza Noor · Computer Lab</t>
+  </si>
+  <si>
+    <t>Social Studies
+Gul Rukh</t>
+  </si>
+  <si>
     <t>Urdu
 Erum Shah</t>
   </si>
@@ -264,18 +304,6 @@
 Ayesha Khan</t>
   </si>
   <si>
-    <t>Computer Studies
-Hamza Noor · Computer Lab</t>
-  </si>
-  <si>
-    <t>Social Studies
-Gul Rukh</t>
-  </si>
-  <si>
-    <t>2
-08:40–09:20</t>
-  </si>
-  <si>
     <t>Computer Studies (continued)</t>
   </si>
   <si>
@@ -283,55 +311,27 @@
 Imran Qureshi</t>
   </si>
   <si>
-    <t>3
-09:20–10:00</t>
-  </si>
-  <si>
-    <t>Science
-Care Fernandes</t>
-  </si>
-  <si>
     <t>Art
 Hamza Noor</t>
   </si>
   <si>
-    <t>4
-10:20–11:00</t>
-  </si>
-  <si>
-    <t>5
-11:00–11:40</t>
-  </si>
-  <si>
-    <t>Mathematics
-Bilal Ahmed</t>
-  </si>
-  <si>
-    <t>6
-11:40–12:20</t>
-  </si>
-  <si>
     <t>–</t>
   </si>
   <si>
-    <t>7
-12:20–13:00</t>
-  </si>
-  <si>
     <t>Grade 6 B · Morning shift</t>
   </si>
   <si>
     <t>Grade 7 A · Morning shift</t>
+  </si>
+  <si>
+    <t>Urdu
+Farhan Iqbal</t>
   </si>
   <si>
     <t>English
 Danish Ali</t>
   </si>
   <si>
-    <t>Urdu
-Farhan Iqbal</t>
-  </si>
-  <si>
     <t>Grade 7 B · Morning shift</t>
   </si>
   <si>
@@ -350,7 +350,7 @@
   </si>
   <si>
     <t>Mathematics
-Grade 7 B</t>
+Grade 6 A</t>
   </si>
   <si>
     <t>Mathematics
@@ -362,10 +362,18 @@
   </si>
   <si>
     <t>Mathematics
+Grade 7 B</t>
+  </si>
+  <si>
+    <t>Care Fernandes · Morning shift</t>
+  </si>
+  <si>
+    <t>Science
+Grade 7 A</t>
+  </si>
+  <si>
+    <t>Science
 Grade 6 A</t>
-  </si>
-  <si>
-    <t>Care Fernandes · Morning shift</t>
   </si>
   <si>
     <t>Science
@@ -373,39 +381,31 @@
   </si>
   <si>
     <t>Science
-Grade 7 A</t>
-  </si>
-  <si>
-    <t>Science
-Grade 6 A</t>
-  </si>
-  <si>
-    <t>Science
 Grade 6 B</t>
   </si>
   <si>
     <t>Danish Ali · Morning shift</t>
+  </si>
+  <si>
+    <t>English
+Grade 7 B</t>
   </si>
   <si>
     <t>English
 Grade 7 A</t>
   </si>
   <si>
-    <t>English
-Grade 7 B</t>
-  </si>
-  <si>
     <t>Erum Shah · Morning shift</t>
+  </si>
+  <si>
+    <t>Urdu
+Grade 6 B</t>
   </si>
   <si>
     <t>Urdu
 Grade 6 A</t>
   </si>
   <si>
-    <t>Urdu
-Grade 6 B</t>
-  </si>
-  <si>
     <t>Farhan Iqbal · Morning shift</t>
   </si>
   <si>
@@ -425,10 +425,6 @@
   </si>
   <si>
     <t>Social Studies
-Grade 7 B</t>
-  </si>
-  <si>
-    <t>Social Studies
 Grade 6 A</t>
   </si>
   <si>
@@ -436,6 +432,10 @@
 Grade 6 B</t>
   </si>
   <si>
+    <t>Social Studies
+Grade 7 B</t>
+  </si>
+  <si>
     <t>Hamza Noor · Morning shift</t>
   </si>
   <si>
@@ -456,7 +456,7 @@
   </si>
   <si>
     <t>Art
-Grade 6 B</t>
+Grade 7 A</t>
   </si>
   <si>
     <t>Art
@@ -464,11 +464,11 @@
   </si>
   <si>
     <t>Art
-Grade 7 A</t>
+Grade 6 A</t>
   </si>
   <si>
     <t>Art
-Grade 6 A</t>
+Grade 6 B</t>
   </si>
   <si>
     <t>Imran Qureshi · Morning shift</t>
@@ -478,32 +478,32 @@
 Grade 6 A · Playground</t>
   </si>
   <si>
+    <t>Physical Education
+Grade 6 B · Playground</t>
+  </si>
+  <si>
+    <t>Physical Education
+Grade 7 B · Playground</t>
+  </si>
+  <si>
+    <t>Physical Education
+Grade 7 A · Playground</t>
+  </si>
+  <si>
+    <t>Islamic Studies
+Grade 6 A</t>
+  </si>
+  <si>
     <t>Islamic Studies
 Grade 7 A</t>
   </si>
   <si>
-    <t>Physical Education
-Grade 6 B · Playground</t>
-  </si>
-  <si>
     <t>Islamic Studies
 Grade 7 B</t>
   </si>
   <si>
     <t>Islamic Studies
-Grade 6 A</t>
-  </si>
-  <si>
-    <t>Physical Education
-Grade 7 A · Playground</t>
-  </si>
-  <si>
-    <t>Islamic Studies
 Grade 6 B</t>
-  </si>
-  <si>
-    <t>Physical Education
-Grade 7 B · Playground</t>
   </si>
   <si>
     <t>Computer Lab · Morning shift</t>
@@ -537,11 +537,11 @@
   </si>
   <si>
     <t>Physical Education
+Grade 7 B · Imran Qureshi</t>
+  </si>
+  <si>
+    <t>Physical Education
 Grade 7 A · Imran Qureshi</t>
-  </si>
-  <si>
-    <t>Physical Education
-Grade 7 B · Imran Qureshi</t>
   </si>
 </sst>
 </file>
@@ -582,14 +582,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF18343F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF18343F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -617,13 +617,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8A33D"/>
+        <fgColor rgb="FF1F6F6B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD17A5B"/>
+        <fgColor rgb="FF6A994E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8A33D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,13 +647,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F6F6B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6A994E"/>
+        <fgColor rgb="FFD17A5B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -709,40 +709,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -751,28 +754,28 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1121,26 +1124,23 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
       <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1148,28 +1148,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1177,28 +1177,31 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1212,13 +1215,13 @@
         <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -1227,7 +1230,7 @@
         <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1241,13 +1244,13 @@
         <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
         <v>31</v>
@@ -1256,7 +1259,7 @@
         <v>35</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1264,28 +1267,28 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" t="s">
-        <v>35</v>
-      </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1293,28 +1296,28 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1322,28 +1325,28 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1351,28 +1354,28 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1380,28 +1383,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1409,28 +1412,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1438,28 +1441,31 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
       </c>
       <c r="E13" t="s">
         <v>42</v>
       </c>
       <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
         <v>15</v>
       </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>16</v>
       </c>
-      <c r="I13" t="s">
-        <v>17</v>
-      </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1467,28 +1473,28 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
       </c>
       <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
         <v>21</v>
       </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1496,13 +1502,10 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
@@ -1511,16 +1514,16 @@
         <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1528,10 +1531,10 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
         <v>42</v>
@@ -1540,7 +1543,7 @@
         <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
         <v>30</v>
@@ -1549,7 +1552,7 @@
         <v>31</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1557,10 +1560,10 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
         <v>42</v>
@@ -1569,7 +1572,7 @@
         <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
         <v>31</v>
@@ -1578,7 +1581,7 @@
         <v>35</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1595,19 +1598,19 @@
         <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
         <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1627,19 +1630,19 @@
         <v>46</v>
       </c>
       <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
         <v>15</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>21</v>
       </c>
-      <c r="H19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" t="s">
-        <v>22</v>
-      </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1659,16 +1662,16 @@
         <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s">
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1676,10 +1679,10 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
         <v>46</v>
@@ -1688,7 +1691,7 @@
         <v>29</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
         <v>30</v>
@@ -1697,7 +1700,7 @@
         <v>31</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1705,10 +1708,10 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
         <v>46</v>
@@ -1717,7 +1720,7 @@
         <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
         <v>31</v>
@@ -1726,7 +1729,7 @@
         <v>35</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1743,19 +1746,19 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
         <v>35</v>
       </c>
       <c r="I23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1763,28 +1766,28 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
         <v>48</v>
       </c>
       <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s">
         <v>15</v>
       </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>16</v>
       </c>
-      <c r="I24" t="s">
-        <v>17</v>
-      </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1792,28 +1795,28 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
         <v>48</v>
       </c>
       <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
         <v>21</v>
       </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" t="s">
-        <v>22</v>
-      </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1821,10 +1824,10 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
@@ -1833,16 +1836,16 @@
         <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s">
         <v>26</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1850,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s">
         <v>48</v>
@@ -1862,7 +1865,7 @@
         <v>29</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
         <v>30</v>
@@ -1871,7 +1874,7 @@
         <v>31</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1879,10 +1882,10 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
         <v>48</v>
@@ -1891,7 +1894,7 @@
         <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
         <v>31</v>
@@ -1900,7 +1903,7 @@
         <v>35</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1917,22 +1920,22 @@
         <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
         <v>15</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>21</v>
       </c>
-      <c r="H29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s">
-        <v>22</v>
-      </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1940,28 +1943,28 @@
         <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1975,13 +1978,13 @@
         <v>33</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
         <v>29</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
         <v>30</v>
@@ -1990,7 +1993,7 @@
         <v>31</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2004,13 +2007,13 @@
         <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s">
         <v>31</v>
@@ -2019,7 +2022,7 @@
         <v>35</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2027,28 +2030,28 @@
         <v>49</v>
       </c>
       <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
         <v>23</v>
       </c>
-      <c r="C33" t="s">
-        <v>24</v>
-      </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2056,28 +2059,28 @@
         <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F34" t="s">
         <v>50</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I34" t="s">
         <v>51</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2085,28 +2088,28 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s">
         <v>15</v>
       </c>
-      <c r="G35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>16</v>
       </c>
-      <c r="I35" t="s">
-        <v>17</v>
-      </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2114,28 +2117,28 @@
         <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
         <v>21</v>
       </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" t="s">
-        <v>17</v>
-      </c>
-      <c r="I36" t="s">
-        <v>22</v>
-      </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2143,28 +2146,28 @@
         <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2172,19 +2175,19 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="C38" t="s">
-        <v>20</v>
-      </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F38" t="s">
         <v>29</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
         <v>30</v>
@@ -2193,7 +2196,7 @@
         <v>31</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2201,19 +2204,19 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
         <v>31</v>
@@ -2222,7 +2225,7 @@
         <v>35</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2230,31 +2233,31 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2262,28 +2265,28 @@
         <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E41" t="s">
         <v>42</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
         <v>15</v>
       </c>
-      <c r="H41" t="s">
-        <v>22</v>
-      </c>
       <c r="I41" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2291,28 +2294,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E42" t="s">
         <v>42</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I42" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2320,28 +2323,28 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
         <v>42</v>
       </c>
       <c r="F43" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2349,28 +2352,28 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E44" t="s">
         <v>42</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I44" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2378,28 +2381,28 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E45" t="s">
         <v>42</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I45" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2407,28 +2410,28 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E46" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="J46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2436,28 +2439,28 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
         <v>46</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
         <v>15</v>
       </c>
-      <c r="H47" t="s">
-        <v>17</v>
-      </c>
       <c r="I47" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2474,19 +2477,19 @@
         <v>46</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2494,28 +2497,28 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
         <v>46</v>
       </c>
       <c r="F49" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2523,28 +2526,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E50" t="s">
         <v>46</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H50" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" t="s">
         <v>31</v>
       </c>
-      <c r="I50" t="s">
-        <v>35</v>
-      </c>
       <c r="J50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2552,31 +2555,28 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
-      </c>
-      <c r="D51" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="J51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2584,28 +2584,31 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
       </c>
       <c r="E52" t="s">
         <v>48</v>
       </c>
       <c r="F52" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G52" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" t="s">
         <v>15</v>
       </c>
-      <c r="H52" t="s">
-        <v>17</v>
-      </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2613,28 +2616,28 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s">
         <v>48</v>
       </c>
       <c r="F53" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I53" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2642,28 +2645,28 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E54" t="s">
         <v>48</v>
       </c>
       <c r="F54" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2671,28 +2674,28 @@
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
         <v>48</v>
       </c>
       <c r="F55" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" t="s">
         <v>31</v>
       </c>
-      <c r="I55" t="s">
-        <v>35</v>
-      </c>
       <c r="J55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2700,28 +2703,28 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s">
         <v>15</v>
       </c>
-      <c r="G56" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>16</v>
       </c>
-      <c r="I56" t="s">
-        <v>17</v>
-      </c>
       <c r="J56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2729,28 +2732,28 @@
         <v>52</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s">
         <v>21</v>
       </c>
-      <c r="G57" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" t="s">
-        <v>17</v>
-      </c>
-      <c r="I57" t="s">
-        <v>22</v>
-      </c>
       <c r="J57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2758,31 +2761,28 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" t="s">
+        <v>53</v>
+      </c>
+      <c r="E58" t="s">
         <v>13</v>
-      </c>
-      <c r="E58" t="s">
-        <v>14</v>
       </c>
       <c r="F58" t="s">
         <v>25</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I58" t="s">
         <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2790,19 +2790,22 @@
         <v>52</v>
       </c>
       <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" t="s">
         <v>23</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F59" t="s">
         <v>29</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
         <v>30</v>
@@ -2811,7 +2814,7 @@
         <v>31</v>
       </c>
       <c r="J59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2819,19 +2822,19 @@
         <v>52</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F60" t="s">
         <v>34</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" t="s">
         <v>31</v>
@@ -2840,7 +2843,7 @@
         <v>35</v>
       </c>
       <c r="J60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2848,28 +2851,28 @@
         <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
         <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
         <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2886,22 +2889,22 @@
         <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" t="s">
         <v>15</v>
       </c>
-      <c r="G62" t="s">
+      <c r="I62" t="s">
         <v>21</v>
       </c>
-      <c r="H62" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62" t="s">
-        <v>22</v>
-      </c>
       <c r="J62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2909,28 +2912,28 @@
         <v>52</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F63" t="s">
         <v>25</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" t="s">
         <v>26</v>
       </c>
       <c r="J63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2938,19 +2941,19 @@
         <v>52</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F64" t="s">
         <v>29</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H64" t="s">
         <v>30</v>
@@ -2959,7 +2962,7 @@
         <v>31</v>
       </c>
       <c r="J64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2967,19 +2970,19 @@
         <v>52</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H65" t="s">
         <v>31</v>
@@ -2988,7 +2991,7 @@
         <v>35</v>
       </c>
       <c r="J65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2996,28 +2999,28 @@
         <v>52</v>
       </c>
       <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" t="s">
+        <v>54</v>
+      </c>
+      <c r="E66" t="s">
+        <v>36</v>
+      </c>
+      <c r="F66" t="s">
+        <v>40</v>
+      </c>
+      <c r="G66" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66" t="s">
         <v>41</v>
       </c>
-      <c r="C66" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" t="s">
-        <v>17</v>
-      </c>
       <c r="J66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3025,28 +3028,28 @@
         <v>52</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E67" t="s">
         <v>42</v>
       </c>
       <c r="F67" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s">
+        <v>14</v>
+      </c>
+      <c r="H67" t="s">
         <v>15</v>
       </c>
-      <c r="H67" t="s">
-        <v>17</v>
-      </c>
       <c r="I67" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3054,28 +3057,31 @@
         <v>52</v>
       </c>
       <c r="B68" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>23</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
       </c>
       <c r="E68" t="s">
         <v>42</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I68" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3083,28 +3089,28 @@
         <v>52</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E69" t="s">
         <v>42</v>
       </c>
       <c r="F69" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I69" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3112,28 +3118,28 @@
         <v>52</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E70" t="s">
         <v>42</v>
       </c>
       <c r="F70" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H70" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" t="s">
         <v>31</v>
       </c>
-      <c r="I70" t="s">
-        <v>35</v>
-      </c>
       <c r="J70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3141,28 +3147,28 @@
         <v>52</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="E71" t="s">
         <v>42</v>
       </c>
       <c r="F71" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" t="s">
         <v>35</v>
       </c>
-      <c r="I71" t="s">
-        <v>39</v>
-      </c>
       <c r="J71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3170,28 +3176,28 @@
         <v>52</v>
       </c>
       <c r="B72" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E72" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F72" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="J72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3199,28 +3205,28 @@
         <v>52</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E73" t="s">
         <v>46</v>
       </c>
       <c r="F73" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" t="s">
         <v>15</v>
       </c>
-      <c r="H73" t="s">
-        <v>17</v>
-      </c>
       <c r="I73" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3233,26 +3239,23 @@
       <c r="C74" t="s">
         <v>12</v>
       </c>
-      <c r="D74" t="s">
-        <v>13</v>
-      </c>
       <c r="E74" t="s">
         <v>46</v>
       </c>
       <c r="F74" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H74" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I74" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3260,28 +3263,28 @@
         <v>52</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E75" t="s">
         <v>46</v>
       </c>
       <c r="F75" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H75" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I75" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3289,7 +3292,7 @@
         <v>52</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C76" t="s">
         <v>53</v>
@@ -3298,19 +3301,19 @@
         <v>46</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H76" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" t="s">
         <v>31</v>
       </c>
-      <c r="I76" t="s">
-        <v>35</v>
-      </c>
       <c r="J76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3318,28 +3321,28 @@
         <v>52</v>
       </c>
       <c r="B77" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E77" t="s">
         <v>46</v>
       </c>
       <c r="F77" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H77" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" t="s">
         <v>35</v>
       </c>
-      <c r="I77" t="s">
-        <v>39</v>
-      </c>
       <c r="J77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3347,28 +3350,28 @@
         <v>52</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E78" t="s">
         <v>48</v>
       </c>
       <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" t="s">
         <v>15</v>
       </c>
-      <c r="G78" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>16</v>
       </c>
-      <c r="I78" t="s">
-        <v>17</v>
-      </c>
       <c r="J78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3376,28 +3379,28 @@
         <v>52</v>
       </c>
       <c r="B79" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E79" t="s">
         <v>48</v>
       </c>
       <c r="F79" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" t="s">
+        <v>14</v>
+      </c>
+      <c r="H79" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" t="s">
         <v>21</v>
       </c>
-      <c r="G79" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" t="s">
-        <v>17</v>
-      </c>
-      <c r="I79" t="s">
-        <v>22</v>
-      </c>
       <c r="J79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3405,10 +3408,10 @@
         <v>52</v>
       </c>
       <c r="B80" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E80" t="s">
         <v>48</v>
@@ -3417,16 +3420,16 @@
         <v>25</v>
       </c>
       <c r="G80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H80" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I80" t="s">
         <v>26</v>
       </c>
       <c r="J80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3434,7 +3437,7 @@
         <v>52</v>
       </c>
       <c r="B81" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C81" t="s">
         <v>54</v>
@@ -3446,7 +3449,7 @@
         <v>29</v>
       </c>
       <c r="G81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H81" t="s">
         <v>30</v>
@@ -3455,7 +3458,7 @@
         <v>31</v>
       </c>
       <c r="J81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3463,10 +3466,10 @@
         <v>52</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C82" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="E82" t="s">
         <v>48</v>
@@ -3475,7 +3478,7 @@
         <v>34</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H82" t="s">
         <v>31</v>
@@ -3484,7 +3487,7 @@
         <v>35</v>
       </c>
       <c r="J82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3492,28 +3495,31 @@
         <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F83" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H83" t="s">
         <v>16</v>
       </c>
       <c r="I83" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3521,28 +3527,28 @@
         <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F84" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" t="s">
+        <v>14</v>
+      </c>
+      <c r="H84" t="s">
         <v>21</v>
       </c>
-      <c r="G84" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" t="s">
-        <v>17</v>
-      </c>
       <c r="I84" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3550,28 +3556,28 @@
         <v>55</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H85" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I85" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J85" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3579,28 +3585,28 @@
         <v>55</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F86" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H86" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3608,28 +3614,28 @@
         <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H87" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -3640,25 +3646,25 @@
         <v>32</v>
       </c>
       <c r="C88" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I88" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="J88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -3666,28 +3672,28 @@
         <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F89" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G89" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" t="s">
         <v>15</v>
       </c>
-      <c r="H89" t="s">
-        <v>17</v>
-      </c>
       <c r="I89" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -3695,28 +3701,28 @@
         <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E90" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H90" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3724,28 +3730,28 @@
         <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F91" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H91" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I91" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3753,28 +3759,28 @@
         <v>55</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C92" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E92" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H92" t="s">
+        <v>30</v>
+      </c>
+      <c r="I92" t="s">
         <v>31</v>
       </c>
-      <c r="I92" t="s">
-        <v>35</v>
-      </c>
       <c r="J92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3782,31 +3788,28 @@
         <v>55</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>12</v>
-      </c>
-      <c r="D93" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F93" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H93" t="s">
+        <v>31</v>
+      </c>
+      <c r="I93" t="s">
         <v>35</v>
       </c>
-      <c r="I93" t="s">
-        <v>39</v>
-      </c>
       <c r="J93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3814,31 +3817,28 @@
         <v>55</v>
       </c>
       <c r="B94" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F94" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G94" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I94" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3846,28 +3846,31 @@
         <v>55</v>
       </c>
       <c r="B95" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C95" t="s">
-        <v>54</v>
+        <v>44</v>
+      </c>
+      <c r="D95" t="s">
+        <v>45</v>
       </c>
       <c r="E95" t="s">
         <v>42</v>
       </c>
       <c r="F95" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G95" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" t="s">
         <v>15</v>
       </c>
-      <c r="H95" t="s">
-        <v>22</v>
-      </c>
       <c r="I95" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3875,28 +3878,28 @@
         <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E96" t="s">
         <v>42</v>
       </c>
       <c r="F96" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I96" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J96" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -3907,25 +3910,25 @@
         <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E97" t="s">
         <v>42</v>
       </c>
       <c r="F97" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H97" t="s">
+        <v>30</v>
+      </c>
+      <c r="I97" t="s">
         <v>31</v>
       </c>
-      <c r="I97" t="s">
-        <v>35</v>
-      </c>
       <c r="J97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -3933,28 +3936,28 @@
         <v>55</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E98" t="s">
         <v>42</v>
       </c>
       <c r="F98" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H98" t="s">
+        <v>31</v>
+      </c>
+      <c r="I98" t="s">
         <v>35</v>
       </c>
-      <c r="I98" t="s">
-        <v>39</v>
-      </c>
       <c r="J98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -3962,28 +3965,28 @@
         <v>55</v>
       </c>
       <c r="B99" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C99" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E99" t="s">
         <v>46</v>
       </c>
       <c r="F99" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" t="s">
+        <v>14</v>
+      </c>
+      <c r="H99" t="s">
         <v>15</v>
       </c>
-      <c r="G99" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
         <v>16</v>
       </c>
-      <c r="I99" t="s">
-        <v>17</v>
-      </c>
       <c r="J99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3991,28 +3994,28 @@
         <v>55</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C100" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E100" t="s">
         <v>46</v>
       </c>
       <c r="F100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" t="s">
         <v>21</v>
       </c>
-      <c r="G100" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" t="s">
-        <v>17</v>
-      </c>
-      <c r="I100" t="s">
-        <v>22</v>
-      </c>
       <c r="J100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -4020,10 +4023,13 @@
         <v>55</v>
       </c>
       <c r="B101" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>54</v>
+        <v>23</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
       </c>
       <c r="E101" t="s">
         <v>46</v>
@@ -4032,16 +4038,16 @@
         <v>25</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I101" t="s">
         <v>26</v>
       </c>
       <c r="J101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -4049,10 +4055,10 @@
         <v>55</v>
       </c>
       <c r="B102" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
         <v>46</v>
@@ -4061,7 +4067,7 @@
         <v>29</v>
       </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H102" t="s">
         <v>30</v>
@@ -4070,7 +4076,7 @@
         <v>31</v>
       </c>
       <c r="J102" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -4078,10 +4084,10 @@
         <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C103" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E103" t="s">
         <v>46</v>
@@ -4090,7 +4096,7 @@
         <v>34</v>
       </c>
       <c r="G103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H103" t="s">
         <v>31</v>
@@ -4099,7 +4105,7 @@
         <v>35</v>
       </c>
       <c r="J103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -4107,28 +4113,28 @@
         <v>55</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E104" t="s">
         <v>46</v>
       </c>
       <c r="F104" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H104" t="s">
         <v>35</v>
       </c>
       <c r="I104" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -4136,28 +4142,28 @@
         <v>55</v>
       </c>
       <c r="B105" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E105" t="s">
         <v>48</v>
       </c>
       <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>14</v>
+      </c>
+      <c r="H105" t="s">
         <v>15</v>
       </c>
-      <c r="G105" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" t="s">
+      <c r="I105" t="s">
         <v>16</v>
       </c>
-      <c r="I105" t="s">
-        <v>17</v>
-      </c>
       <c r="J105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -4165,28 +4171,28 @@
         <v>55</v>
       </c>
       <c r="B106" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C106" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E106" t="s">
         <v>48</v>
       </c>
       <c r="F106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" t="s">
+        <v>14</v>
+      </c>
+      <c r="H106" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" t="s">
         <v>21</v>
       </c>
-      <c r="G106" t="s">
-        <v>15</v>
-      </c>
-      <c r="H106" t="s">
-        <v>17</v>
-      </c>
-      <c r="I106" t="s">
-        <v>22</v>
-      </c>
       <c r="J106" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -4194,10 +4200,10 @@
         <v>55</v>
       </c>
       <c r="B107" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="E107" t="s">
         <v>48</v>
@@ -4206,16 +4212,16 @@
         <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I107" t="s">
         <v>26</v>
       </c>
       <c r="J107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -4223,10 +4229,10 @@
         <v>55</v>
       </c>
       <c r="B108" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C108" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="E108" t="s">
         <v>48</v>
@@ -4235,7 +4241,7 @@
         <v>29</v>
       </c>
       <c r="G108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H108" t="s">
         <v>30</v>
@@ -4244,7 +4250,7 @@
         <v>31</v>
       </c>
       <c r="J108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -4252,13 +4258,10 @@
         <v>55</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C109" t="s">
-        <v>12</v>
-      </c>
-      <c r="D109" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E109" t="s">
         <v>48</v>
@@ -4267,7 +4270,7 @@
         <v>34</v>
       </c>
       <c r="G109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H109" t="s">
         <v>31</v>
@@ -4276,7 +4279,7 @@
         <v>35</v>
       </c>
       <c r="J109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4290,7 +4293,7 @@
   <dimension ref="A1:AH8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="34" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -4303,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -4312,7 +4315,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -4346,487 +4349,487 @@
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" ht="30" customHeight="1">
       <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>34</v>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>63</v>
-      </c>
+      <c r="A4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="11"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>59</v>
+      <c r="I4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="O4" s="11"/>
       <c r="P4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>62</v>
+        <v>67</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="V4" s="11"/>
-      <c r="W4" s="13" t="s">
+      <c r="W4" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="X4" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="AB4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE4" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Y4" s="14" t="s">
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Z4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC4" s="11"/>
-      <c r="AD4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE4" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF4" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH4" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34">
-      <c r="A5" s="4" t="s">
+      <c r="M5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="O5" s="11"/>
+      <c r="P5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="S5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="T5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="V5" s="11"/>
+      <c r="W5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="X5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y5" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="U5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="W5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z5" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA5" s="9" t="s">
-        <v>62</v>
+      <c r="Z5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA5" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
-      <c r="AD5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH5" s="7" t="s">
-        <v>60</v>
-      </c>
+      <c r="AD5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH5" s="11"/>
     </row>
     <row r="6" spans="1:34">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="C6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>70</v>
       </c>
+      <c r="G6" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="M6" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" s="11"/>
+      <c r="P6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="8" t="s">
+      <c r="Q6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" s="11"/>
+      <c r="W6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="R6" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" s="8" t="s">
+      <c r="X6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH6" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="A7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="T6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="U6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="V6" s="11"/>
-      <c r="W6" s="8" t="s">
+      <c r="H7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="X6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF6" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG6" s="8" t="s">
+      <c r="O7" s="11"/>
+      <c r="P7" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="R7" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="X7" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AH6" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34">
-      <c r="A7" s="4" t="s">
+      <c r="Y7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC7" s="11"/>
+      <c r="AD7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG7" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="11"/>
-      <c r="P7" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="V7" s="11"/>
-      <c r="W7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="X7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA7" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH7" s="5" t="s">
-        <v>58</v>
+      <c r="AH7" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:34">
-      <c r="A8" s="4" t="s">
-        <v>72</v>
+      <c r="A8" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -4879,24 +4882,24 @@
   <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="6" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="6" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>42</v>
@@ -4909,133 +4912,133 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A3" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>80</v>
+      <c r="A3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A4" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="19" t="s">
+      <c r="A4" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A6" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="E6" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A5" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A7" s="15" t="s">
+      <c r="E7" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>91</v>
+      <c r="E8" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A9" s="15" t="s">
-        <v>92</v>
+      <c r="A9" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="25" t="s">
-        <v>91</v>
+      <c r="F9" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5045,13 +5048,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>42</v>
@@ -5064,133 +5067,133 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="11"/>
+      <c r="A14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>87</v>
+      </c>
       <c r="E14" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>76</v>
+        <v>82</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A15" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>76</v>
+      <c r="D15" s="21" t="s">
+        <v>86</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="D19" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A17" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A20" s="15" t="s">
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="26" t="s">
         <v>92</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="25" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5200,13 +5203,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>42</v>
@@ -5219,133 +5222,133 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="21" t="s">
+      <c r="A25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="C25" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A26" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="19" t="s">
+      <c r="C27" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="23" t="s">
+      <c r="D28" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A28" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="18" t="s">
+      <c r="C29" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A29" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A30" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>91</v>
+      <c r="E30" s="11"/>
+      <c r="F30" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A31" s="15" t="s">
-        <v>92</v>
+      <c r="A31" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="25" t="s">
-        <v>91</v>
+      <c r="F31" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -5355,13 +5358,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>42</v>
@@ -5374,133 +5377,133 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="24" t="s">
+      <c r="A36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A37" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="21" t="s">
+      <c r="E37" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A38" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" s="19" t="s">
+      <c r="C38" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="E37" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A38" s="15" t="s">
+      <c r="D38" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="23" t="s">
+      <c r="F38" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A39" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="17" t="s">
+      <c r="C41" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" s="17" t="s">
+      <c r="F41" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A42" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="E39" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A40" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A41" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F41" s="25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A42" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
-      <c r="F42" s="25" t="s">
-        <v>91</v>
+      <c r="F42" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -5513,8 +5516,8 @@
   <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="6" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="6" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5524,13 +5527,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>42</v>
@@ -5543,97 +5546,97 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A3" s="15" t="s">
-        <v>75</v>
+      <c r="A3" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>100</v>
-      </c>
+      <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A4" s="15" t="s">
-        <v>81</v>
+      <c r="A4" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A6" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="11"/>
-    </row>
-    <row r="5" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A5" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="18" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="E7" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>90</v>
+      <c r="A8" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="25" t="s">
-        <v>91</v>
+      <c r="D8" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A9" s="15" t="s">
-        <v>92</v>
+      <c r="A9" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="25" t="s">
-        <v>91</v>
+      <c r="F9" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5643,13 +5646,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>42</v>
@@ -5662,117 +5665,117 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="24" t="s">
+      <c r="A14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="11"/>
+      <c r="D14" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A15" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="24" t="s">
+      <c r="E17" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="24" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F18" s="17" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A16" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A17" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="24" t="s">
+    <row r="19" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>91</v>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>92</v>
+      <c r="A20" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
-      <c r="F20" s="25" t="s">
-        <v>91</v>
+      <c r="F20" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5782,13 +5785,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>42</v>
@@ -5801,109 +5804,109 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
+      <c r="A25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>108</v>
+      </c>
       <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="22" t="s">
+      <c r="E25" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A26" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="22" t="s">
+    <row r="27" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="18" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="22" t="s">
+    <row r="28" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A28" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="22" t="s">
+      <c r="C29" s="11"/>
+      <c r="D29" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A29" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="22" t="s">
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A30" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>91</v>
+      <c r="E30" s="11"/>
+      <c r="F30" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A31" s="15" t="s">
-        <v>92</v>
+      <c r="A31" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="25" t="s">
-        <v>91</v>
+      <c r="F31" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -5913,13 +5916,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>42</v>
@@ -5932,20 +5935,18 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>75</v>
+      <c r="A36" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="18" t="s">
-        <v>112</v>
-      </c>
+      <c r="E36" s="11"/>
       <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A37" s="15" t="s">
-        <v>81</v>
+      <c r="A37" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -5954,75 +5955,77 @@
       <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A38" s="15" t="s">
-        <v>84</v>
+      <c r="A38" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E39" s="11"/>
+      <c r="F39" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="18" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="E40" s="23" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A39" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="18" t="s">
+      <c r="F40" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="18" t="s">
+    </row>
+    <row r="41" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="18" t="s">
+      <c r="F41" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A42" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="23" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A40" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-    </row>
-    <row r="41" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A41" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A42" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
-      <c r="F42" s="25" t="s">
-        <v>91</v>
+      <c r="F42" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -6032,13 +6035,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>42</v>
@@ -6051,93 +6054,93 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A47" s="15" t="s">
-        <v>75</v>
+      <c r="A47" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B47" s="11"/>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="11"/>
+      <c r="D47" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A48" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="F47" s="11"/>
-    </row>
-    <row r="48" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A48" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B48" s="11"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
+      <c r="D48" s="22" t="s">
+        <v>116</v>
+      </c>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A49" s="15" t="s">
-        <v>84</v>
+      <c r="A49" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="17" t="s">
+      <c r="E49" s="22" t="s">
         <v>115</v>
       </c>
+      <c r="F49" s="22" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A50" s="15" t="s">
-        <v>87</v>
+      <c r="A50" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
+      <c r="C50" s="22" t="s">
+        <v>115</v>
+      </c>
       <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="17" t="s">
+      <c r="E50" s="22" t="s">
         <v>116</v>
       </c>
+      <c r="F50" s="22" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A51" s="15" t="s">
-        <v>88</v>
+      <c r="A51" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="17" t="s">
-        <v>115</v>
-      </c>
+      <c r="D51" s="11"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A52" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>115</v>
-      </c>
+      <c r="A52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="11"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="17" t="s">
-        <v>116</v>
-      </c>
+      <c r="D52" s="11"/>
       <c r="E52" s="11"/>
-      <c r="F52" s="25" t="s">
-        <v>91</v>
+      <c r="F52" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A53" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>116</v>
-      </c>
+      <c r="A53" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
-      <c r="F53" s="25" t="s">
-        <v>91</v>
+      <c r="F53" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -6147,13 +6150,13 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>42</v>
@@ -6166,93 +6169,93 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A58" s="15" t="s">
-        <v>75</v>
+      <c r="A58" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
+      <c r="C58" s="22" t="s">
+        <v>118</v>
+      </c>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
     </row>
     <row r="59" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A59" s="15" t="s">
-        <v>81</v>
+      <c r="A59" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
+      <c r="F59" s="22" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A60" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B60" s="11"/>
+      <c r="A60" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>119</v>
+      </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
+      <c r="F60" s="22" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A61" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B61" s="17" t="s">
+      <c r="A61" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="22" t="s">
         <v>118</v>
       </c>
       <c r="C61" s="11"/>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="11"/>
+      <c r="E61" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F61" s="11"/>
+    </row>
+    <row r="62" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A62" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E61" s="11"/>
-      <c r="F61" s="17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A62" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C62" s="11"/>
-      <c r="D62" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>119</v>
-      </c>
+      <c r="F62" s="11"/>
     </row>
     <row r="63" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A63" s="15" t="s">
-        <v>90</v>
+      <c r="A63" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F63" s="25" t="s">
-        <v>91</v>
+      <c r="D63" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63" s="11"/>
+      <c r="F63" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A64" s="15" t="s">
-        <v>92</v>
+      <c r="A64" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
       <c r="E64" s="11"/>
-      <c r="F64" s="25" t="s">
-        <v>91</v>
+      <c r="F64" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -6262,13 +6265,13 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>42</v>
@@ -6281,101 +6284,101 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A69" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>121</v>
-      </c>
+      <c r="A69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F69" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="F69" s="20" t="s">
+    </row>
+    <row r="70" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A70" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="21" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A70" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70" s="20" t="s">
+      <c r="E70" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F70" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C70" s="20" t="s">
+    </row>
+    <row r="71" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A71" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="D70" s="11"/>
-      <c r="E70" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A71" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B71" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="C71" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D71" s="11"/>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
     </row>
     <row r="72" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A72" s="15" t="s">
-        <v>87</v>
+      <c r="A72" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="B72" s="11"/>
-      <c r="C72" s="20" t="s">
-        <v>124</v>
+      <c r="C72" s="21" t="s">
+        <v>122</v>
       </c>
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
     </row>
     <row r="73" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A73" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
+      <c r="A73" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>121</v>
+      </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
     </row>
     <row r="74" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A74" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="20" t="s">
-        <v>121</v>
-      </c>
+      <c r="A74" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" s="11"/>
       <c r="E74" s="11"/>
-      <c r="F74" s="25" t="s">
-        <v>91</v>
+      <c r="F74" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="26" t="s">
         <v>92</v>
-      </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E75" s="11"/>
-      <c r="F75" s="25" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -6385,13 +6388,13 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>42</v>
@@ -6404,62 +6407,60 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A80" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B80" s="19" t="s">
+      <c r="A80" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B80" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="D80" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E80" s="19" t="s">
+      <c r="E80" s="20" t="s">
         <v>129</v>
       </c>
       <c r="F80" s="11"/>
     </row>
     <row r="81" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A81" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>82</v>
+      <c r="A81" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>89</v>
       </c>
       <c r="F81" s="11"/>
     </row>
     <row r="82" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A82" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B82" s="23" t="s">
+      <c r="A82" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" s="11"/>
+      <c r="C82" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="D82" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="D82" s="23" t="s">
+      <c r="E82" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="E82" s="23" t="s">
-        <v>133</v>
-      </c>
       <c r="F82" s="11"/>
     </row>
     <row r="83" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A83" s="15" t="s">
-        <v>87</v>
+      <c r="A83" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -6468,37 +6469,39 @@
       <c r="F83" s="11"/>
     </row>
     <row r="84" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A84" s="15" t="s">
-        <v>88</v>
+      <c r="A84" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
+      <c r="C84" s="25" t="s">
+        <v>133</v>
+      </c>
       <c r="D84" s="11"/>
       <c r="E84" s="11"/>
       <c r="F84" s="11"/>
     </row>
     <row r="85" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A85" s="15" t="s">
-        <v>90</v>
+      <c r="A85" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
       <c r="E85" s="11"/>
-      <c r="F85" s="25" t="s">
-        <v>91</v>
+      <c r="F85" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A86" s="15" t="s">
-        <v>92</v>
+      <c r="A86" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
       <c r="E86" s="11"/>
-      <c r="F86" s="25" t="s">
-        <v>91</v>
+      <c r="F86" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -6508,13 +6511,13 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>42</v>
@@ -6527,109 +6530,109 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A91" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B91" s="16" t="s">
+      <c r="A91" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C91" s="11"/>
-      <c r="D91" s="21" t="s">
+      <c r="E91" s="11"/>
+      <c r="F91" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="E91" s="11"/>
-      <c r="F91" s="16" t="s">
+    </row>
+    <row r="92" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A92" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" s="19" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A92" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B92" s="21" t="s">
+      <c r="C92" s="11"/>
+      <c r="D92" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="C92" s="11"/>
-      <c r="D92" s="16" t="s">
+      <c r="E92" s="11"/>
+      <c r="F92" s="24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A93" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="11"/>
+      <c r="D93" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E93" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="21" t="s">
+      <c r="F93" s="11"/>
+    </row>
+    <row r="94" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A94" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C94" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D94" s="11"/>
+      <c r="E94" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A95" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B95" s="11"/>
+      <c r="C95" s="24" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A93" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B93" s="16" t="s">
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="F93" s="21" t="s">
+    </row>
+    <row r="96" spans="1:6" ht="44.25" customHeight="1">
+      <c r="A96" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C96" s="19" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A94" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B94" s="11"/>
-      <c r="C94" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="D94" s="11"/>
-      <c r="E94" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="F94" s="11"/>
-    </row>
-    <row r="95" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A95" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B95" s="11"/>
-      <c r="C95" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D95" s="11"/>
-      <c r="E95" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F95" s="16" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A96" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B96" s="11"/>
-      <c r="C96" s="16" t="s">
-        <v>142</v>
       </c>
       <c r="D96" s="11"/>
       <c r="E96" s="11"/>
-      <c r="F96" s="25" t="s">
-        <v>91</v>
+      <c r="F96" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A97" s="15" t="s">
-        <v>92</v>
+      <c r="A97" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
       <c r="E97" s="11"/>
-      <c r="F97" s="25" t="s">
-        <v>91</v>
+      <c r="F97" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -6642,8 +6645,8 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="6" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="6" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6653,13 +6656,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>42</v>
@@ -6672,44 +6675,44 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A3" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>147</v>
       </c>
       <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A4" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>82</v>
+      <c r="A4" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>89</v>
       </c>
       <c r="F4" s="11"/>
     </row>
     <row r="5" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A5" s="15" t="s">
-        <v>84</v>
+      <c r="A5" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -6718,8 +6721,8 @@
       <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>87</v>
+      <c r="A6" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -6728,8 +6731,8 @@
       <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>88</v>
+      <c r="A7" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -6738,27 +6741,27 @@
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>90</v>
+      <c r="A8" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="25" t="s">
-        <v>91</v>
+      <c r="F8" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A9" s="15" t="s">
-        <v>92</v>
+      <c r="A9" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="25" t="s">
-        <v>91</v>
+      <c r="F9" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6768,13 +6771,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>42</v>
@@ -6787,93 +6790,93 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
       <c r="E14" s="11"/>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="19" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A15" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="11"/>
+      <c r="A15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>151</v>
+      </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="16" t="s">
-        <v>150</v>
+      <c r="D15" s="19" t="s">
+        <v>152</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A16" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="16" t="s">
+      <c r="A16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>151</v>
-      </c>
       <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A17" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="11"/>
+      <c r="A17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>152</v>
+      </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>88</v>
+      <c r="A18" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
-      <c r="F18" s="16" t="s">
-        <v>152</v>
-      </c>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>90</v>
+      <c r="A19" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="B19" s="11"/>
-      <c r="C19" s="16" t="s">
-        <v>152</v>
+      <c r="C19" s="19" t="s">
+        <v>150</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="25" t="s">
-        <v>91</v>
+      <c r="F19" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="44.25" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>92</v>
+      <c r="A20" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
-      <c r="F20" s="25" t="s">
-        <v>91</v>
+      <c r="F20" s="26" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
